--- a/doc/source/_static/data/supporting_files/Nomenclature_and_formulas.xlsx
+++ b/doc/source/_static/data/supporting_files/Nomenclature_and_formulas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns8="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:ns9="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzorinaldi/Documents/GitHub/MARIO/doc/source/_static/data/supporting_files/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878D9818-DF8A-F74C-93B0-71F1559B842D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <ns1:AlternateContent>
+    <ns1:Choice Requires="x15">
+      <ns2:absPath url="/Users/lorenzorinaldi/Documents/GitHub/MARIO/doc/source/_static/data/supporting_files/"/>
+    </ns1:Choice>
+  </ns1:AlternateContent>
+  <ns3:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878D9818-DF8A-F74C-93B0-71F1559B842D}" ns4:coauthVersionLast="47" ns4:coauthVersionMax="47" ns5:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17660" activeTab="3" xr2:uid="{191C6CC1-D0C2-3B4B-A0D5-6A4A3794157A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17660" activeTab="3" ns6:uid="{191C6CC1-D0C2-3B4B-A0D5-6A4A3794157A}"/>
   </bookViews>
   <sheets>
     <sheet name="Matrices" sheetId="6" r:id="rId1"/>
@@ -18,25 +18,26 @@
     <sheet name="IOT" sheetId="3" r:id="rId3"/>
     <sheet name="SUT_IT" sheetId="4" r:id="rId4"/>
     <sheet name="SUT_PT" sheetId="5" r:id="rId5"/>
+    <sheet name="Read me" sheetId="7" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Matrices!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <ns8:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <ns9:calcFeatures>
+        <ns9:feature name="microsoft.com:RD"/>
+        <ns9:feature name="microsoft.com:Single"/>
+        <ns9:feature name="microsoft.com:FV"/>
+        <ns9:feature name="microsoft.com:CNMTM"/>
+        <ns9:feature name="microsoft.com:LET_WF"/>
+        <ns9:feature name="microsoft.com:LAMBDA_WF"/>
+        <ns9:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </ns9:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -685,12 +686,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0E+00"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="@"/>
+    <numFmt numFmtId="167" formatCode="@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="13" ns2:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -727,8 +730,50 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF302820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF302820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF302820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF302820"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -843,8 +888,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF302820"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF302820"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -881,12 +948,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="4"/>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1031,19 +1114,59 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="4" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="20" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="5" xfId="3"/>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="23" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{367C7BCA-BA7C-6441-BCAB-F120F399731F}"/>
+    <cellStyle name="Normal 2" xfId="1" ns3:uid="{367C7BCA-BA7C-6441-BCAB-F120F399731F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns4:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns5:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -14900,6 +15023,86 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/source_notice7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFF0783C"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="100" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <c r="A1" s="64" t="str">
+        <v>Read me</v>
+      </c>
+      <c r="B1" s="64" t="str">
+        <v>MARIO nomenclature and formulas</v>
+      </c>
+    </row>
+    <row r="2" ht="15" hidden="0" customHeight="1">
+      <c r="A2" s="62" t="str">
+        <v>Contents</v>
+      </c>
+      <c r="B2" s="65" t="str">
+        <v>MARIO names and matrix calculations on packaged demonstration IOT and SUT tables. No third-party MRIO observations.</v>
+      </c>
+    </row>
+    <row r="3" ht="24" hidden="0" customHeight="1">
+      <c r="A3" s="62" t="str">
+        <v>How to use</v>
+      </c>
+      <c r="B3" s="65" t="str">
+        <v>Matrices and Indices define MARIO names. IOT, SUT_IT and SUT_PT demonstrate calculations on packaged test tables and their technology assumptions.</v>
+      </c>
+    </row>
+    <row r="4" ht="15" hidden="0" customHeight="1">
+      <c r="A4" s="62" t="str">
+        <v>Source</v>
+      </c>
+      <c r="B4" s="65" t="str">
+        <v>https://github.com/it-is-me-mario/MARIO</v>
+      </c>
+    </row>
+    <row r="5" ht="15" hidden="0" customHeight="1">
+      <c r="A5" s="62" t="str">
+        <v>Attribution</v>
+      </c>
+      <c r="B5" s="65" t="str">
+        <v>MARIO documentation and packaged demonstration tables.</v>
+      </c>
+    </row>
+    <row r="6" ht="15" hidden="0" customHeight="1">
+      <c r="A6" s="62" t="str">
+        <v>Licence</v>
+      </c>
+      <c r="B6" s="65" t="str">
+        <v>GNU GPL version 3; see the MARIO repository licence.</v>
+      </c>
+    </row>
+    <row r="7" ht="15" hidden="0" customHeight="1">
+      <c r="A7" s="62" t="str">
+        <v>Licence URL</v>
+      </c>
+      <c r="B7" s="65" t="str">
+        <v>https://github.com/it-is-me-mario/MARIO/blob/main/LICENSE</v>
+      </c>
+    </row>
+    <row r="8" ht="15" hidden="0" customHeight="1">
+      <c r="A8" s="62" t="str">
+        <v>Scope</v>
+      </c>
+      <c r="B8" s="65" t="str">
+        <v>Demonstration calculations, not observations of an actual economy. All original formulas and cached results are retained.</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">

--- a/doc/source/_static/data/supporting_files/Nomenclature_and_formulas.xlsx
+++ b/doc/source/_static/data/supporting_files/Nomenclature_and_formulas.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns8="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:ns9="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:ns6="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:ns8="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:ns9="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" ns1:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <ns1:AlternateContent>
@@ -686,7 +686,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0E+00"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
